--- a/WWW.xlsx
+++ b/WWW.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\1.Finance\Anaylsen\Models\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4DE02BCF-C7EF-4F5E-8EE8-FDC6EFE087AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7900D946-E6BC-45D1-BBF3-8E7C07BC477F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20925" activeTab="1" xr2:uid="{BF6AB992-A367-41FE-B952-7A79782DC4DD}"/>
+    <workbookView xWindow="19095" yWindow="0" windowWidth="19410" windowHeight="20985" xr2:uid="{BF6AB992-A367-41FE-B952-7A79782DC4DD}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -230,13 +230,19 @@
     <numFmt numFmtId="164" formatCode="#,##0.0;\(#,##0.0\)"/>
     <numFmt numFmtId="165" formatCode="#,##0.00;\(#,##0.00\)"/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="11" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -319,28 +325,31 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="9" fontId="6" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="2" applyFont="1"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1"/>
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="2" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="9" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="9" fontId="3" fillId="0" borderId="0" xfId="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -703,7 +712,7 @@
         <v>2</v>
       </c>
       <c r="J2" s="2">
-        <v>15.35</v>
+        <v>19.989999999999998</v>
       </c>
     </row>
     <row r="3" spans="1:11" x14ac:dyDescent="0.2">
@@ -711,10 +720,10 @@
         <v>3</v>
       </c>
       <c r="J3" s="3">
-        <v>81.989541000000003</v>
-      </c>
-      <c r="K3" s="15" t="s">
-        <v>57</v>
+        <v>82.066338999999999</v>
+      </c>
+      <c r="K3" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.2">
@@ -723,7 +732,7 @@
       </c>
       <c r="J4" s="3">
         <f>+J2*J3</f>
-        <v>1258.5394543499999</v>
+        <v>1640.5061166099999</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.2">
@@ -731,10 +740,10 @@
         <v>5</v>
       </c>
       <c r="J5" s="3">
-        <v>119.6</v>
-      </c>
-      <c r="K5" s="15" t="s">
-        <v>57</v>
+        <v>158.5</v>
+      </c>
+      <c r="K5" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.2">
@@ -742,10 +751,10 @@
         <v>6</v>
       </c>
       <c r="J6" s="3">
-        <v>546.9</v>
-      </c>
-      <c r="K6" s="15" t="s">
-        <v>57</v>
+        <v>547.1</v>
+      </c>
+      <c r="K6" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.2">
@@ -754,7 +763,7 @@
       </c>
       <c r="J7" s="3">
         <f>+J4-J5+J6</f>
-        <v>1685.8394543499999</v>
+        <v>2029.1061166099998</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.2">
@@ -887,7 +896,9 @@
       <c r="K3" s="3">
         <v>371.6</v>
       </c>
-      <c r="L3" s="3"/>
+      <c r="L3" s="3">
+        <v>388.4</v>
+      </c>
       <c r="M3" s="3"/>
       <c r="N3" s="3"/>
       <c r="O3" s="3"/>
@@ -969,7 +980,9 @@
       <c r="K4" s="3">
         <v>75.7</v>
       </c>
-      <c r="L4" s="3"/>
+      <c r="L4" s="3">
+        <v>105.8</v>
+      </c>
       <c r="M4" s="3"/>
       <c r="N4" s="3"/>
       <c r="O4" s="3"/>
@@ -1051,7 +1064,9 @@
       <c r="K5" s="3">
         <v>10.3</v>
       </c>
-      <c r="L5" s="3"/>
+      <c r="L5" s="3">
+        <v>12.2</v>
+      </c>
       <c r="M5" s="3"/>
       <c r="N5" s="3"/>
       <c r="O5" s="3"/>
@@ -1133,7 +1148,9 @@
       <c r="K6" s="3">
         <v>99.1</v>
       </c>
-      <c r="L6" s="3"/>
+      <c r="L6" s="3">
+        <v>111.7</v>
+      </c>
       <c r="M6" s="3"/>
       <c r="N6" s="3"/>
       <c r="O6" s="3"/>
@@ -1222,7 +1239,9 @@
         <f>+K8-K6</f>
         <v>358.5</v>
       </c>
-      <c r="L7" s="3"/>
+      <c r="L7" s="3">
+        <v>394.7</v>
+      </c>
       <c r="M7" s="3"/>
       <c r="N7" s="3"/>
       <c r="O7" s="3"/>
@@ -1310,7 +1329,9 @@
       <c r="K8" s="7">
         <v>457.6</v>
       </c>
-      <c r="L8" s="7"/>
+      <c r="L8" s="7">
+        <v>506.4</v>
+      </c>
       <c r="M8" s="7"/>
       <c r="N8" s="7"/>
       <c r="O8" s="3"/>
@@ -1394,7 +1415,9 @@
       <c r="K9" s="3">
         <v>239.8</v>
       </c>
-      <c r="L9" s="3"/>
+      <c r="L9" s="3">
+        <v>271.10000000000002</v>
+      </c>
       <c r="M9" s="3"/>
       <c r="N9" s="3"/>
       <c r="O9" s="3"/>
@@ -1454,7 +1477,7 @@
         <v>25</v>
       </c>
       <c r="C10" s="3">
-        <f t="shared" ref="C10:K10" si="0">+C8-C9</f>
+        <f t="shared" ref="C10:L10" si="0">+C8-C9</f>
         <v>181.39999999999998</v>
       </c>
       <c r="D10" s="3">
@@ -1489,7 +1512,10 @@
         <f t="shared" si="0"/>
         <v>217.8</v>
       </c>
-      <c r="L10" s="3"/>
+      <c r="L10" s="3">
+        <f t="shared" si="0"/>
+        <v>235.29999999999995</v>
+      </c>
       <c r="M10" s="3"/>
       <c r="N10" s="3"/>
       <c r="O10" s="3"/>
@@ -1580,7 +1606,9 @@
       <c r="K11" s="3">
         <v>182.7</v>
       </c>
-      <c r="L11" s="3"/>
+      <c r="L11" s="3">
+        <v>187.4</v>
+      </c>
       <c r="M11" s="3"/>
       <c r="N11" s="3"/>
       <c r="O11" s="3"/>
@@ -1664,7 +1692,9 @@
       <c r="K12" s="3">
         <v>0</v>
       </c>
-      <c r="L12" s="3"/>
+      <c r="L12" s="3">
+        <v>0.6</v>
+      </c>
       <c r="M12" s="3"/>
       <c r="N12" s="3"/>
       <c r="O12" s="3"/>
@@ -1748,7 +1778,9 @@
       <c r="K13" s="3">
         <v>0</v>
       </c>
-      <c r="L13" s="3"/>
+      <c r="L13" s="3">
+        <v>0</v>
+      </c>
       <c r="M13" s="3"/>
       <c r="N13" s="3"/>
       <c r="O13" s="3"/>
@@ -1832,7 +1864,9 @@
       <c r="K14" s="3">
         <v>1.2</v>
       </c>
-      <c r="L14" s="3"/>
+      <c r="L14" s="3">
+        <v>0</v>
+      </c>
       <c r="M14" s="3"/>
       <c r="N14" s="3"/>
       <c r="O14" s="3"/>
@@ -1927,7 +1961,10 @@
         <f>+K10-SUM(K11:K14)</f>
         <v>33.900000000000034</v>
       </c>
-      <c r="L15" s="3"/>
+      <c r="L15" s="3">
+        <f>+L10-SUM(L11:L14)</f>
+        <v>47.299999999999955</v>
+      </c>
       <c r="M15" s="3"/>
       <c r="N15" s="3"/>
       <c r="O15" s="3"/>
@@ -2018,7 +2055,9 @@
       <c r="K16" s="3">
         <v>6.5</v>
       </c>
-      <c r="L16" s="3"/>
+      <c r="L16" s="3">
+        <v>7.1</v>
+      </c>
       <c r="M16" s="3"/>
       <c r="N16" s="3"/>
       <c r="O16" s="3"/>
@@ -2102,7 +2141,9 @@
       <c r="K17" s="3">
         <v>-0.2</v>
       </c>
-      <c r="L17" s="3"/>
+      <c r="L17" s="3">
+        <v>-0.6</v>
+      </c>
       <c r="M17" s="3"/>
       <c r="N17" s="3"/>
       <c r="O17" s="3"/>
@@ -2197,7 +2238,10 @@
         <f>+K15-SUM(K16:K17)</f>
         <v>27.600000000000033</v>
       </c>
-      <c r="L18" s="3"/>
+      <c r="L18" s="3">
+        <f>+L15-SUM(L16:L17)</f>
+        <v>40.799999999999955</v>
+      </c>
       <c r="M18" s="3"/>
       <c r="N18" s="3"/>
       <c r="O18" s="3"/>
@@ -2288,7 +2332,9 @@
       <c r="K19" s="3">
         <v>5.2</v>
       </c>
-      <c r="L19" s="3"/>
+      <c r="L19" s="3">
+        <v>7.9</v>
+      </c>
       <c r="M19" s="3"/>
       <c r="N19" s="3"/>
       <c r="O19" s="3"/>
@@ -2348,7 +2394,7 @@
         <v>34</v>
       </c>
       <c r="C20" s="3">
-        <f t="shared" ref="C20:K20" si="6">+C18-C19</f>
+        <f t="shared" ref="C20:L20" si="6">+C18-C19</f>
         <v>-13.700000000000022</v>
       </c>
       <c r="D20" s="3">
@@ -2383,7 +2429,10 @@
         <f t="shared" si="6"/>
         <v>22.400000000000034</v>
       </c>
-      <c r="L20" s="3"/>
+      <c r="L20" s="3">
+        <f t="shared" si="6"/>
+        <v>32.899999999999956</v>
+      </c>
       <c r="M20" s="3"/>
       <c r="N20" s="3"/>
       <c r="O20" s="3"/>
@@ -2474,7 +2523,9 @@
       <c r="K21" s="3">
         <v>2.2000000000000002</v>
       </c>
-      <c r="L21" s="3"/>
+      <c r="L21" s="3">
+        <v>1.7</v>
+      </c>
       <c r="M21" s="3"/>
       <c r="N21" s="3"/>
       <c r="O21" s="3"/>
@@ -2534,7 +2585,7 @@
         <v>36</v>
       </c>
       <c r="C22" s="3">
-        <f t="shared" ref="C22:K22" si="8">+C20-C21</f>
+        <f t="shared" ref="C22:L22" si="8">+C20-C21</f>
         <v>-14.500000000000023</v>
       </c>
       <c r="D22" s="3">
@@ -2569,7 +2620,10 @@
         <f t="shared" si="8"/>
         <v>20.200000000000035</v>
       </c>
-      <c r="L22" s="3"/>
+      <c r="L22" s="3">
+        <f t="shared" si="8"/>
+        <v>31.199999999999957</v>
+      </c>
       <c r="M22" s="3"/>
       <c r="N22" s="3"/>
       <c r="O22" s="3"/>
@@ -2693,7 +2747,7 @@
         <v>37</v>
       </c>
       <c r="C24" s="8">
-        <f t="shared" ref="C24:K24" si="10">+C22/C25</f>
+        <f t="shared" ref="C24:L24" si="10">+C22/C25</f>
         <v>-0.18170426065162937</v>
       </c>
       <c r="D24" s="8">
@@ -2728,7 +2782,10 @@
         <f t="shared" si="10"/>
         <v>0.24724602203182416</v>
       </c>
-      <c r="L24" s="8"/>
+      <c r="L24" s="8">
+        <f t="shared" si="10"/>
+        <v>0.38048780487804823</v>
+      </c>
       <c r="M24" s="8"/>
       <c r="N24" s="8"/>
       <c r="O24" s="3"/>
@@ -2819,7 +2876,9 @@
       <c r="K25" s="3">
         <v>81.7</v>
       </c>
-      <c r="L25" s="3"/>
+      <c r="L25" s="3">
+        <v>82</v>
+      </c>
       <c r="M25" s="3"/>
       <c r="N25" s="3"/>
       <c r="O25" s="3"/>
@@ -2952,14 +3011,17 @@
         <v>0.10699717602761227</v>
       </c>
       <c r="J27" s="13" t="e">
-        <f t="shared" ref="J27:K32" si="15">+J3/F3-1</f>
+        <f t="shared" ref="J27:L32" si="15">+J3/F3-1</f>
         <v>#DIV/0!</v>
       </c>
       <c r="K27" s="13">
         <f t="shared" si="15"/>
         <v>0.13743495561677399</v>
       </c>
-      <c r="L27" s="13"/>
+      <c r="L27" s="13">
+        <f t="shared" si="15"/>
+        <v>9.2545710267229131E-2</v>
+      </c>
       <c r="M27" s="13"/>
       <c r="N27" s="13"/>
       <c r="O27" s="3"/>
@@ -3052,7 +3114,10 @@
         <f t="shared" si="15"/>
         <v>1.2032085561497485E-2</v>
       </c>
-      <c r="L28" s="13"/>
+      <c r="L28" s="13">
+        <f t="shared" si="15"/>
+        <v>-1.5813953488372112E-2</v>
+      </c>
       <c r="M28" s="13"/>
       <c r="N28" s="13"/>
       <c r="O28" s="3"/>
@@ -3145,7 +3210,10 @@
         <f t="shared" si="15"/>
         <v>-4.629629629629628E-2</v>
       </c>
-      <c r="L29" s="13"/>
+      <c r="L29" s="13">
+        <f t="shared" si="15"/>
+        <v>8.9285714285714191E-2</v>
+      </c>
       <c r="M29" s="13"/>
       <c r="N29" s="13"/>
       <c r="O29" s="3"/>
@@ -3238,7 +3306,10 @@
         <f t="shared" si="15"/>
         <v>-0.68629313073757525</v>
       </c>
-      <c r="L30" s="13"/>
+      <c r="L30" s="13">
+        <f t="shared" si="15"/>
+        <v>-0.69194704908990623</v>
+      </c>
       <c r="M30" s="13"/>
       <c r="N30" s="13"/>
       <c r="O30" s="3"/>
@@ -3331,7 +3402,10 @@
         <f t="shared" si="15"/>
         <v>2.7188796680497922</v>
       </c>
-      <c r="L31" s="13"/>
+      <c r="L31" s="13">
+        <f t="shared" si="15"/>
+        <v>2.5367383512544803</v>
+      </c>
       <c r="M31" s="13"/>
       <c r="N31" s="13"/>
       <c r="O31" s="3"/>
@@ -3424,7 +3498,10 @@
         <f t="shared" si="15"/>
         <v>0.10987145282561239</v>
       </c>
-      <c r="L32" s="10"/>
+      <c r="L32" s="10">
+        <f t="shared" si="15"/>
+        <v>6.7903838043019693E-2</v>
+      </c>
       <c r="M32" s="10"/>
       <c r="N32" s="10"/>
       <c r="O32" s="7"/>
@@ -3523,10 +3600,13 @@
         <v>0.47033816425120767</v>
       </c>
       <c r="K33" s="9">
-        <f t="shared" ref="K33" si="21">+K10/K8</f>
+        <f t="shared" ref="K33:L33" si="21">+K10/K8</f>
         <v>0.47596153846153844</v>
       </c>
-      <c r="L33" s="9"/>
+      <c r="L33" s="9">
+        <f t="shared" si="21"/>
+        <v>0.46465244865718791</v>
+      </c>
       <c r="M33" s="9"/>
       <c r="N33" s="9"/>
       <c r="O33" s="3"/>
@@ -3631,7 +3711,10 @@
         <f>+K15/K8</f>
         <v>7.4082167832167908E-2</v>
       </c>
-      <c r="L34" s="9"/>
+      <c r="L34" s="9">
+        <f>+L15/L8</f>
+        <v>9.3404423380726617E-2</v>
+      </c>
       <c r="M34" s="9"/>
       <c r="N34" s="9"/>
       <c r="O34" s="3"/>
@@ -3733,10 +3816,13 @@
         <v>0.1935483870967743</v>
       </c>
       <c r="K35" s="9">
-        <f t="shared" ref="K35" si="26">+K19/K18</f>
+        <f t="shared" ref="K35:L35" si="26">+K19/K18</f>
         <v>0.18840579710144906</v>
       </c>
-      <c r="L35" s="9"/>
+      <c r="L35" s="9">
+        <f t="shared" si="26"/>
+        <v>0.19362745098039238</v>
+      </c>
       <c r="M35" s="9"/>
       <c r="N35" s="9"/>
       <c r="O35" s="3"/>
